--- a/data/daily/2026-10/2026-10-12.xlsx
+++ b/data/daily/2026-10/2026-10-12.xlsx
@@ -1245,14 +1245,64 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,60 +1342,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1500,27 +1500,77 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,79 +1578,29 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -2596,24 +2596,28 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16254</v>
+        <v>16255</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물용 만족도 — 센스 있고 고급스러운 선물로 받는 사람의 만족도가 높음</t>
+          <t>우수한 피로 회복 효과 — 유난히 피곤한 날 섭취 시 피로감이 줄어들고 힘이 나는 효과가 느껴짐</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>피로 회복 체감 — 섭취 후 피로감이 덜하고 기운이 나는 효과 체감함</t>
+          <t>선물용으로 높은 만족도 — 유명한 명품 비타민으로 주는 사람과 받는 사람 모두 만족도가 높음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>간편한 섭취 및 맛 — 간편하게 섭취하기 편하고 맛도 좋음</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>편리한 섭취 및 빠른 배송 — 포장이 튼튼하게 배송되며 간편하게 섭취할 수 있어 편리함</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>다소 부담스러운 가격 — 제품 가격대가 은근히 비싸게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -2655,26 +2659,26 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15589</v>
+        <v>15590</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>선물용 만족도 — 피로 회복 및 건강 응원용 선물로 주고받기 좋음</t>
+          <t>확실한 피로 개선 효과 — 누적된 피로 완화 및 체력 보충에 도움이 되어 힘이 남</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>피로 회복 체감 — 누적된 피로 회복과 기운 보충에 효과적임</t>
+          <t>선물용으로 우수한 만족도 — 응원이나 생일 선물용으로 주고받기 적합함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>간편한 섭취 편의 — 환절기나 지칠 때 간편하게 챙겨 먹기 편함</t>
+          <t>간편한 섭취 방식 — 환절기 건강 관리에 간편하게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>배송 지연 불만 — 배송이 너무 늦게 도착하여 아쉬움</t>
+          <t>아쉬운 배송 속도 — 배송이 지연되어 너무 늦게 도착함</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -2718,21 +2722,21 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>활력 증진 효과 — 섭취 후 다음 날 피로가 덜하고 즉각적인 활력이 느껴짐</t>
+          <t>체감되는 활력 증진 — 복용 시 다음 날 피로가 덜하고 몸의 활력이 달라짐</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>선물용 적합성 — 포장이 꼼꼼하고 선물용으로 주고받기 만족스러움</t>
+          <t>선물하기 좋은 제품 — 선물로 받거나 전달할 때 기분이 좋고 만족스러움</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>진한 액상 제형 — 다른 액상 비타민 대비 맛이 진해서 만족스러움</t>
+          <t>꼼꼼한 포장과 빠른 배송 — 배송이 빠르고 꼼꼼하게 포장되어 도착함</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2781,17 +2785,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득한 젤리 제형이라 간식처럼 맛있게 섭취 가능함</t>
+          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득하여 간식처럼 부담 없이 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>섭취 용이성 — 알약을 잘 삼키지 못하는 사람도 부담 없이 챙겨 먹기 편함</t>
+          <t>쉽고 간편한 섭취 — 알약을 잘 못 먹는 사람도 젤리 제형이라 편하게 챙겨 먹음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>선물용 디자인 — 패키지가 귀엽고 포장이 예뻐 선물용으로 만족스러움</t>
+          <t>귀여운 패키지 디자인 — 패키지와 증정품 키캡 디자인이 귀엽고 기분 좋은 선물이 됨</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2840,22 +2844,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>피로 개선 효과 — 복용 후 체력 저하와 피로감이 확연히 줄어드는 느낌을 받음</t>
+          <t>빠른 피로 회복 효과 — 며칠만 복용해도 오후 체력 저하와 피로감이 확연히 줄어듦</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>우수한 휴대성 — 개별 포장으로 출근길이나 외출 시 간편하게 휴대 가능함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>편리한 섭취 방식 — 물 없이도 간편하게 먹을 수 있고 목넘김이 좋음</t>
-        </is>
-      </c>
+          <t>우수한 휴대성과 편리성 — 개별 포장이 견고하고 물 없이도 간편하게 섭취할 수 있음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>배송 포장 부실 — 쇼핑백 없이 박스에 본품만 배송되어 포장에 아쉬움 남음</t>
+          <t>미흡한 선물용 배송 포장 — 쇼핑백이 미동봉되고 박스에 그냥 배송되어 포장이 아쉬움</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2903,22 +2903,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>간편한 휴대 섭취 — 한 포씩 소포장되어 외출 시 휴대 및 간편 섭취에 용이함</t>
+          <t>확실한 컨디션 개선 — 섭취 후 피로 회복에 도움이 되고 아침 컨디션이 달라짐</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>피로 회복 도움 — 복용 후 다음 날 아침 컨디션과 피로 회복에 도움 됨</t>
+          <t>간편한 휴대 및 섭취 — 한 포씩 소포장되어 외출 시 챙기기 편하고 맛도 부담 없음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>고급스러운 구성 — 알약과 음료 세트 구성 및 포장이 깔끔하여 선물용으로 적합함</t>
+          <t>고급스러운 제품 포장 — 알약과 음료 세트 구성에 포장이 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>적은 세트 구성 — 소포장 구성이라 선물이 풍성해 보이지 않을 수 있음</t>
+          <t>작아 보이는 소포장 양 — 소포장이라 풍성한 선물 느낌은 다소 부족할 수 있음</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -2962,21 +2962,21 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 고급 박스와 종이가방 포장으로 명절 및 기념일 선물로 훌륭함</t>
+          <t>환절기 면역 및 컨디션 관리 — 환절기 활력 충전 및 체력 관리에 도움을 줌</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>휴대 및 복용 편의 — 한 병씩 구성되어 출근 시 가볍게 챙겨 먹기 편함</t>
+          <t>예쁜 선물 포장 패키지 — 포장이 예쁘게 되어 있어 명절이나 생일 선물용으로 좋음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>활력 충전 효과 — 매일 섭취하며 지친 체력과 환절기 면역 관리에 도움 됨</t>
+          <t>하루 한 병 간편 섭취 — 개별 병으로 구성되어 출근 시 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3025,17 +3025,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>남녀 맞춤 구성 — 성별에 맞춰 선택할 수 있는 옵션이 있어 만족스러움</t>
+          <t>쓴맛 없는 간편한 섭취 — 특유의 쓴맛이 없어 먹기 편하고 휴대성이 좋음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>복용 편의 및 맛 — 특유의 쓴맛이 없고 진한 맛으로 먹기 편함</t>
+          <t>성별 맞춤형 구획 — 남성과 여성용 비타민이 구분되어 맞춤 영양 관리가 가능함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>체력 및 활력 보충 — 직장인 피로 완화와 파워 충전에 즉각적인 도움 됨</t>
+          <t>직장인 활력 충전 효과 — 피로 해소에 확실한 도움을 주고 활력을 돋워줌</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3080,26 +3080,26 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>빠른 활력 회복 — 섭취 후 즉각적으로 피로가 풀리고 기운이 남</t>
+          <t>즉각적인 활력 및 피로 회복 — 섭취 즉시 피로 회복과 활력 충전 효과가 느껴짐</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 각 잡힌 깔끔하고 특색 있는 포장으로 선물용 가치 높음</t>
+          <t>각 잡힌 고급 포장 — 깔끔하고 정갈한 포장 박스 구성으로 선물용에 적합함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>넉넉한 용량 — 기존 액상 앰플 대비 용량이 넉넉하여 만족스러움</t>
+          <t>먹기 편한 액상 타입 — 넉넉한 용량에 액상 제형으로 섭취하기 용이함</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>복용 시 목메임 — 분말 제형 탓에 섭취 시 목이 메여 물이 필요함</t>
+          <t>분말 섭취 시 목메임 — 분말 제형 특성상 섭취 후 목이 메어 물이 필요할 수 있음</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3143,21 +3143,21 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>29838</v>
+        <v>29848</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>간편한 복합 제형 — 액상과 알약이 함께 있어 물 없이도 간편하게 복용 가능함</t>
+          <t>물 없이 먹는 편의성 — 별도의 물이 필요 없어 언제 어디서나 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>알약 크기 적당 — 정제 크기가 두껍지 않아 목넘김이 수월함</t>
+          <t>맛있는 음료 및 젤리 맛 — 거부감 없는 맛으로 기운을 차리는 데 도움이 됨</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>활력 개선 체감 — 아침 피로 개선 및 일상 활력 회복에 도움 됨</t>
+          <t>건강을 챙기는 좋은 선물 — 수험생이나 직장인 등 건강을 신경 쓰는 이들에게 전달하기 좋음</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29,600원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3202,26 +3202,22 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>맛있는 효소 풍미 — 베리말차 맛 등 거부감 없이 맛있게 먹기 좋음</t>
+          <t>맛있는 풍미와 높은 만족도 — 베리말차 맛 등 맛있게 섭취할 수 있어 종류별 재구매 의사가 높음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>푸짐한 사은품 — 포토카드 및 다양한 사은품 구성이 만족스러움</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>편리한 섭취 방식 — 간편하게 챙겨 먹기 편한 제형임</t>
-        </is>
-      </c>
+          <t>간편함과 빠른 배송 — 섭취가 간편하며 배송 상태가 매우 우수함</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>아쉬운 1포 용량 — 맛에 비해 1포당 용량이 다소 작게 느껴짐</t>
+          <t>다소 적은 내용물 양 — 맛은 좋으나 1포당 용량이 다소 적게 느껴짐</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3269,22 +3265,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 플리츠백 등 패키지와 포장이 고급스러워 선물용으로 훌륭함</t>
+          <t>고급스러운 선물용 포장 — 오간자 에디션 및 패키지 포장이 예쁘고 고급스러워 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>맛과 간편함 — 비린 맛 없이 맛있으며 하루 한 병 간편하게 섭취 가능함</t>
+          <t>맛있는 앰플 제형 — 맛이 매우 우수하여 부담 없이 꾸준히 먹기 좋음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>피로 완화 체감 — 섭취 후 피로감이 덜해지는 느낌을 받음</t>
+          <t>피로 완화 및 피부 기대감 — 피로감이 덜하며 환절기 피부 탄력 개선 효과가 기대됨</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>다소 비싼 가격 — 가격대가 높아 할인 행사 시기에만 구매하게 됨</t>
+          <t>비싼 가격대 — 가격대가 다소 높아 할인 기간에 구매를 선호하게 됨</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3301,53 +3297,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +9포 +파로저당견과류바 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261008170829_70d90b6ebfe240ff87e96b3497f02811.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>1697</v>
+        <v>21</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>속 편한 소화감 — 섭취 후 속이 편안해지고 소화 관리에 도움 됨</t>
+          <t>탁월한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 아침 숙취와 늘어짐이 확연히 줄어듦</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>알찬 사은품 증정 — 견과류바와 추가 파우치 등 사은품 구성이 풍성함</t>
+          <t>휴대하기 편한 스틱 형태 — 개별 스틱 포장으로 물 없이 모임이나 술자리에 들고 가기 편함</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>선물용 포장 만족 — 포장이 고급스러워 선물용 및 자가 섭취용 모두 적합함</t>
+          <t>고급스러운 보라색 패키지 — 쇼핑백과 정품 스티커 등 패키징이 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>가격 할인 아쉬움 — 지속적인 재구매를 위해 추가적인 가격 할인이 필요함</t>
+          <t>한약재 특유의 맛 — 쌍화탕이나 한약재 같은 쓴맛이 포함되어 호불호가 갈릴 수 있음</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3356,7 +3352,7 @@
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3364,58 +3360,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +9포 +파로저당견과류바 증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/6352718</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261008170829_70d90b6ebfe240ff87e96b3497f02811.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>1915</v>
+        <v>1697</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>운동 수행능력 향상 — 세트 후반 반복 횟수 유지 및 수행 개수 증대에 도움 됨</t>
+          <t>속이 편안한 소화 작용 — 섭취 시 속이 편안해지고 소화에 도움을 줌</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>우수한 풀림성 — 가루 뭉침 없이 부드럽게 잘 녹아 음료에 타 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>체력 부담 완화 — 운동 시 덜 지치고 피로 부담이 줄어듦</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>알찬 사은품 및 고급 포장 — 포장이 고급스럽고 증정용 견과류바와 추가 효소가 포함되어 만족스러움</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>가격 할인 필요성 — 구매 부담을 줄이기 위한 세일 행사가 더 자주 요구됨</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3423,53 +3419,53 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>숙취 해소 체감 — 음주 전후 섭취 시 다음 날 숙취와 무거운 느낌이 덜함</t>
+          <t>촉촉하고 풍부한 맛 — 닭가슴살이 촉촉하며 다양한 양념 맛으로 질리지 않고 맛있음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>우수한 휴대성 — 스틱 개별 포장이라 모임이나 술자리에 챙겨가기 편리함</t>
+          <t>간편한 데우기 조리 — 전자레인지로 간편하게 데워 먹을 수 있어 식단 관리에 용이함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 쇼핑백이 포함된 깔끔한 패키지로 선물용 만족도 높음</t>
+          <t>가성비와 빠른 배송 — 할인 행사로 저렴하게 구매 가능하며 배송이 빠르고 튼튼함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>진한 한약재 맛 — 쌍화탕이나 한약 같은 쓴맛이 있어 호불호가 갈릴 수 있음</t>
+          <t>이물질(뼈) 혼입 발생 — 섭취 과정에서 단단한 뼈 조각이 씹히는 현상이 발생함</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -3478,7 +3474,7 @@
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3486,7 +3482,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3496,38 +3492,38 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10908258</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>1183</v>
+        <v>1915</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>부담 없는 매실맛 — 물에 잘 풀리고 매실맛이 맛있어 운동 중 마시기 좋음</t>
+          <t>운동 수행 능력 향상 — 섭취 후 피로감이 줄고 운동 세트 후반까지 수행 개수가 유지됨</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>운동 퍼포먼스 향상 — 수분 및 아미노산 보충으로 운동 수행능력 향상 체감함</t>
+          <t>잘 녹는 부드러운 입자 — 가루 뭉침 없이 음료나 보충제에 부드럽게 잘 녹아 마시기 편함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>넉넉한 용량 구성 — 양이 넉넉하여 꾸준히 섭취하기에 좋음</t>
+          <t>헬스 입문자 맞춤 선물 — 운동하는 사람에게 실용적이며 부작용 없이 신뢰도가 높음</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -3537,7 +3533,7 @@
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3545,55 +3541,51 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/10908258</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261007162359_e049ea90261c452fae5a5a6f6ff7e802.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>1535</v>
+        <v>1183</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>알찬 활력 세트 구성 — 아르기닌과 밀크씨슬 조합으로 일상과 운동 활력 관리에 최적임</t>
+          <t>맛있고 부담 없는 풍미 — 매실 맛 등 맛과 향이 좋아 운동 중 물 대신 마시기 편함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>피로 개선 체감 — 아침 기상 시 몸이 가볍고 운동 집중도가 향상됨</t>
+          <t>잘 풀리는 가루 제형 — 가루가 뭉치지 않고 잘 풀어져 음용 시 편리함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>쇼핑백 동봉 선물성 — 쇼핑백이 포함되어 지인이나 동료 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>쇼핑백 불량 배송 — 증정 쇼핑백에 손잡이 끈이 누락되어 배송됨</t>
-        </is>
-      </c>
+          <t>운동 효과 체감 상승 — 섭취 시 전해질 보충 및 수행 능력 향상 차이가 크게 느껴짐</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
@@ -3608,51 +3600,51 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
+          <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>218</v>
+        <v>1535</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>비리지 않은 맛 — 단백질 특유의 텁텁함이나 비린 맛 없이 초코우유처럼 달콤함</t>
+          <t>확실한 활력 및 피로 개선 — 아침 피로감이 줄어들고 운동 집중도 및 하루 활력이 향상됨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>간편한 포만감 — 운동 후나 간식 대용으로 간편하게 마시기 좋고 배가 든든함</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>선물용 호응도 — 지인 및 부모님 운동 선물용으로 호불호 없이 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>알찬 2개월분 세트 구성 — 아르기닌과 밀크씨슬을 함께 챙길 수 있는 효율적인 구성임</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>쇼핑백 부품 누락 — 증정용 쇼핑백의 끈이 안 달려서 배송되는 경우가 있음</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
@@ -3667,62 +3659,58 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"닭가슴살 완벽세트" 보냉백+한끼통살 닭가슴살 15팩 세트</t>
+          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10892246</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260518144708_605bd6c19e8d44cf8257b6dd6cb12c59.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>218</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>다양한 맛 구성 — 소시지 및 여러 양념 맛이 포함되어 물리지 않고 식사 가능함</t>
+          <t>비린 맛 없는 달콤함 — 단백질 음료 특유의 비린 맛이나 텁텁함 없이 달콤하고 깔끔함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>실용적인 보냉백 — 도시락 휴대가 가능한 넉넉한 크기의 보냉백을 증정함</t>
+          <t>든든한 포만감 제공 — 섭취 시 포만감이 느껴져 간식 대용이나 운동 후 마시기 좋음</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 식감 — 퍽퍽하지 않고 일반 음식처럼 맛있게 즐길 수 있음</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>이물질(뼈) 발견 — 섭취 중 단단한 뼈 조각이 씹히는 문제 발생함</t>
-        </is>
-      </c>
+          <t>빠른 배송 및 증정 혜택 — 배송이 빠르고 추가 팩 증정이 있어 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3730,53 +3718,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>"닭가슴살 완벽세트" 보냉백+한끼통살 닭가슴살 15팩 세트</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23,900원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/10892246</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260518144708_605bd6c19e8d44cf8257b6dd6cb12c59.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>908</v>
+        <v>15</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>속 편한 소화감 — 섭취 후 더부룩함이 완화되고 소화가 잘됨</t>
+          <t>넉넉한 크기의 보냉백 증정 — 도시락용으로 들고 다니기 좋은 큼직한 보냉가방이 제공됨</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>달콤한 옥수수맛 — 콘스프처럼 달콤하고 고소하여 거부감 없이 맛있음</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>가성비 및 사은품 — 가격 대비 구성이 푸짐하고 씬칩 등 사은품 증정이 만족스러움</t>
-        </is>
-      </c>
+          <t>다양하고 풍부한 구성 — 여러 맛과 소세지 종류를 다양하게 체험할 수 있어 질리지 않음</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>맛 변화 아쉬움 — 이전 구매분에 비해 맛에 다소 차이가 느껴짐</t>
+          <t>뼈 조각 혼입 문제 — 닭가슴살 제품 내부에서 단단한 뼈가 씹히는 경우가 있음</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -4100,13 +4084,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16254</v>
+        <v>16255</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15589</v>
+        <v>15590</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>6514</v>
@@ -4118,16 +4102,16 @@
         <v>8748</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>783</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>29838</v>
+        <v>29848</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -4138,72 +4122,71 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물용 만족도 — 센스 있고 고급스러운 선물로 받는 사람의 만족도가 높음
-피로 회복 체감 — 섭취 후 피로감이 덜하고 기운이 나는 효과 체감함
-간편한 섭취 및 맛 — 간편하게 섭취하기 편하고 맛도 좋음</t>
+          <t>우수한 피로 회복 효과 — 유난히 피곤한 날 섭취 시 피로감이 줄어들고 힘이 나는 효과가 느껴짐
+선물용으로 높은 만족도 — 유명한 명품 비타민으로 주는 사람과 받는 사람 모두 만족도가 높음
+편리한 섭취 및 빠른 배송 — 포장이 튼튼하게 배송되며 간편하게 섭취할 수 있어 편리함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>선물용 만족도 — 피로 회복 및 건강 응원용 선물로 주고받기 좋음
-피로 회복 체감 — 누적된 피로 회복과 기운 보충에 효과적임
-간편한 섭취 편의 — 환절기나 지칠 때 간편하게 챙겨 먹기 편함</t>
+          <t>확실한 피로 개선 효과 — 누적된 피로 완화 및 체력 보충에 도움이 되어 힘이 남
+선물용으로 우수한 만족도 — 응원이나 생일 선물용으로 주고받기 적합함
+간편한 섭취 방식 — 환절기 건강 관리에 간편하게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>활력 증진 효과 — 섭취 후 다음 날 피로가 덜하고 즉각적인 활력이 느껴짐
-선물용 적합성 — 포장이 꼼꼼하고 선물용으로 주고받기 만족스러움
-진한 액상 제형 — 다른 액상 비타민 대비 맛이 진해서 만족스러움</t>
+          <t>체감되는 활력 증진 — 복용 시 다음 날 피로가 덜하고 몸의 활력이 달라짐
+선물하기 좋은 제품 — 선물로 받거나 전달할 때 기분이 좋고 만족스러움
+꼼꼼한 포장과 빠른 배송 — 배송이 빠르고 꼼꼼하게 포장되어 도착함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득한 젤리 제형이라 간식처럼 맛있게 섭취 가능함
-섭취 용이성 — 알약을 잘 삼키지 못하는 사람도 부담 없이 챙겨 먹기 편함
-선물용 디자인 — 패키지가 귀엽고 포장이 예뻐 선물용으로 만족스러움</t>
+          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득하여 간식처럼 부담 없이 맛있게 먹기 좋음
+쉽고 간편한 섭취 — 알약을 잘 못 먹는 사람도 젤리 제형이라 편하게 챙겨 먹음
+귀여운 패키지 디자인 — 패키지와 증정품 키캡 디자인이 귀엽고 기분 좋은 선물이 됨</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>피로 개선 효과 — 복용 후 체력 저하와 피로감이 확연히 줄어드는 느낌을 받음
-우수한 휴대성 — 개별 포장으로 출근길이나 외출 시 간편하게 휴대 가능함
-편리한 섭취 방식 — 물 없이도 간편하게 먹을 수 있고 목넘김이 좋음</t>
+          <t>빠른 피로 회복 효과 — 며칠만 복용해도 오후 체력 저하와 피로감이 확연히 줄어듦
+우수한 휴대성과 편리성 — 개별 포장이 견고하고 물 없이도 간편하게 섭취할 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>간편한 휴대 섭취 — 한 포씩 소포장되어 외출 시 휴대 및 간편 섭취에 용이함
-피로 회복 도움 — 복용 후 다음 날 아침 컨디션과 피로 회복에 도움 됨
-고급스러운 구성 — 알약과 음료 세트 구성 및 포장이 깔끔하여 선물용으로 적합함</t>
+          <t>확실한 컨디션 개선 — 섭취 후 피로 회복에 도움이 되고 아침 컨디션이 달라짐
+간편한 휴대 및 섭취 — 한 포씩 소포장되어 외출 시 챙기기 편하고 맛도 부담 없음
+고급스러운 제품 포장 — 알약과 음료 세트 구성에 포장이 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 포장 — 고급 박스와 종이가방 포장으로 명절 및 기념일 선물로 훌륭함
-휴대 및 복용 편의 — 한 병씩 구성되어 출근 시 가볍게 챙겨 먹기 편함
-활력 충전 효과 — 매일 섭취하며 지친 체력과 환절기 면역 관리에 도움 됨</t>
+          <t>환절기 면역 및 컨디션 관리 — 환절기 활력 충전 및 체력 관리에 도움을 줌
+예쁜 선물 포장 패키지 — 포장이 예쁘게 되어 있어 명절이나 생일 선물용으로 좋음
+하루 한 병 간편 섭취 — 개별 병으로 구성되어 출근 시 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>남녀 맞춤 구성 — 성별에 맞춰 선택할 수 있는 옵션이 있어 만족스러움
-복용 편의 및 맛 — 특유의 쓴맛이 없고 진한 맛으로 먹기 편함
-체력 및 활력 보충 — 직장인 피로 완화와 파워 충전에 즉각적인 도움 됨</t>
+          <t>쓴맛 없는 간편한 섭취 — 특유의 쓴맛이 없어 먹기 편하고 휴대성이 좋음
+성별 맞춤형 구획 — 남성과 여성용 비타민이 구분되어 맞춤 영양 관리가 가능함
+직장인 활력 충전 효과 — 피로 해소에 확실한 도움을 주고 활력을 돋워줌</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>빠른 활력 회복 — 섭취 후 즉각적으로 피로가 풀리고 기운이 남
-고급스러운 패키지 — 각 잡힌 깔끔하고 특색 있는 포장으로 선물용 가치 높음
-넉넉한 용량 — 기존 액상 앰플 대비 용량이 넉넉하여 만족스러움</t>
+          <t>즉각적인 활력 및 피로 회복 — 섭취 즉시 피로 회복과 활력 충전 효과가 느껴짐
+각 잡힌 고급 포장 — 깔끔하고 정갈한 포장 박스 구성으로 선물용에 적합함
+먹기 편한 액상 타입 — 넉넉한 용량에 액상 제형으로 섭취하기 용이함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>간편한 복합 제형 — 액상과 알약이 함께 있어 물 없이도 간편하게 복용 가능함
-알약 크기 적당 — 정제 크기가 두껍지 않아 목넘김이 수월함
-활력 개선 체감 — 아침 피로 개선 및 일상 활력 회복에 도움 됨</t>
+          <t>물 없이 먹는 편의성 — 별도의 물이 필요 없어 언제 어디서나 챙겨 먹기 편함
+맛있는 음료 및 젤리 맛 — 거부감 없는 맛으로 기운을 차리는 데 도움이 됨
+건강을 챙기는 좋은 선물 — 수험생이나 직장인 등 건강을 신경 쓰는 이들에게 전달하기 좋음</t>
         </is>
       </c>
     </row>
@@ -4213,29 +4196,33 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>다소 부담스러운 가격 — 제품 가격대가 은근히 비싸게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>배송 지연 불만 — 배송이 너무 늦게 도착하여 아쉬움</t>
+          <t>아쉬운 배송 속도 — 배송이 지연되어 너무 늦게 도착함</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>배송 포장 부실 — 쇼핑백 없이 박스에 본품만 배송되어 포장에 아쉬움 남음</t>
+          <t>미흡한 선물용 배송 포장 — 쇼핑백이 미동봉되고 박스에 그냥 배송되어 포장이 아쉬움</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>적은 세트 구성 — 소포장 구성이라 선물이 풍성해 보이지 않을 수 있음</t>
+          <t>작아 보이는 소포장 양 — 소포장이라 풍성한 선물 느낌은 다소 부족할 수 있음</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>복용 시 목메임 — 분말 제형 탓에 섭취 시 목이 메여 물이 필요함</t>
+          <t>분말 섭취 시 목메임 — 분말 제형 특성상 섭취 후 목이 메어 물이 필요할 수 있음</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -4451,37 +4438,37 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -4503,42 +4490,42 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>삼대오백</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>삼대오백</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>익스트림</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>셀렉스</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
         </is>
       </c>
     </row>
@@ -4560,42 +4547,42 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +9포 +파로저당견과류바 증정</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>[선물/운동]삼대오백 필수 아미노산 EAA 300g 헬스 직장인 수분보충</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>쇼핑백 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>"닭가슴살 완벽세트" 보냉백+한끼통살 닭가슴살 15팩 세트</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
     </row>
@@ -4643,34 +4630,34 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>755</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>1697</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="G19" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>1915</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="H19" s="3" t="n">
+      <c r="I19" s="3" t="n">
         <v>1183</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="J19" s="3" t="n">
         <v>1535</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="K19" s="3" t="n">
         <v>218</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="L19" s="3" t="n">
         <v>15</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>908</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4681,72 +4668,68 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 효소 풍미 — 베리말차 맛 등 거부감 없이 맛있게 먹기 좋음
-푸짐한 사은품 — 포토카드 및 다양한 사은품 구성이 만족스러움
-편리한 섭취 방식 — 간편하게 챙겨 먹기 편한 제형임</t>
+          <t>맛있는 풍미와 높은 만족도 — 베리말차 맛 등 맛있게 섭취할 수 있어 종류별 재구매 의사가 높음
+간편함과 빠른 배송 — 섭취가 간편하며 배송 상태가 매우 우수함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 플리츠백 등 패키지와 포장이 고급스러워 선물용으로 훌륭함
-맛과 간편함 — 비린 맛 없이 맛있으며 하루 한 병 간편하게 섭취 가능함
-피로 완화 체감 — 섭취 후 피로감이 덜해지는 느낌을 받음</t>
+          <t>고급스러운 선물용 포장 — 오간자 에디션 및 패키지 포장이 예쁘고 고급스러워 선물용으로 훌륭함
+맛있는 앰플 제형 — 맛이 매우 우수하여 부담 없이 꾸준히 먹기 좋음
+피로 완화 및 피부 기대감 — 피로감이 덜하며 환절기 피부 탄력 개선 효과가 기대됨</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화감 — 섭취 후 속이 편안해지고 소화 관리에 도움 됨
-알찬 사은품 증정 — 견과류바와 추가 파우치 등 사은품 구성이 풍성함
-선물용 포장 만족 — 포장이 고급스러워 선물용 및 자가 섭취용 모두 적합함</t>
+          <t>탁월한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 아침 숙취와 늘어짐이 확연히 줄어듦
+휴대하기 편한 스틱 형태 — 개별 스틱 포장으로 물 없이 모임이나 술자리에 들고 가기 편함
+고급스러운 보라색 패키지 — 쇼핑백과 정품 스티커 등 패키징이 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>운동 수행능력 향상 — 세트 후반 반복 횟수 유지 및 수행 개수 증대에 도움 됨
-우수한 풀림성 — 가루 뭉침 없이 부드럽게 잘 녹아 음료에 타 먹기 편함
-체력 부담 완화 — 운동 시 덜 지치고 피로 부담이 줄어듦</t>
+          <t>속이 편안한 소화 작용 — 섭취 시 속이 편안해지고 소화에 도움을 줌
+알찬 사은품 및 고급 포장 — 포장이 고급스럽고 증정용 견과류바와 추가 효소가 포함되어 만족스러움</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>숙취 해소 체감 — 음주 전후 섭취 시 다음 날 숙취와 무거운 느낌이 덜함
-우수한 휴대성 — 스틱 개별 포장이라 모임이나 술자리에 챙겨가기 편리함
-고급스러운 패키지 — 쇼핑백이 포함된 깔끔한 패키지로 선물용 만족도 높음</t>
+          <t>촉촉하고 풍부한 맛 — 닭가슴살이 촉촉하며 다양한 양념 맛으로 질리지 않고 맛있음
+간편한 데우기 조리 — 전자레인지로 간편하게 데워 먹을 수 있어 식단 관리에 용이함
+가성비와 빠른 배송 — 할인 행사로 저렴하게 구매 가능하며 배송이 빠르고 튼튼함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 매실맛 — 물에 잘 풀리고 매실맛이 맛있어 운동 중 마시기 좋음
-운동 퍼포먼스 향상 — 수분 및 아미노산 보충으로 운동 수행능력 향상 체감함
-넉넉한 용량 구성 — 양이 넉넉하여 꾸준히 섭취하기에 좋음</t>
+          <t>운동 수행 능력 향상 — 섭취 후 피로감이 줄고 운동 세트 후반까지 수행 개수가 유지됨
+잘 녹는 부드러운 입자 — 가루 뭉침 없이 음료나 보충제에 부드럽게 잘 녹아 마시기 편함
+헬스 입문자 맞춤 선물 — 운동하는 사람에게 실용적이며 부작용 없이 신뢰도가 높음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>알찬 활력 세트 구성 — 아르기닌과 밀크씨슬 조합으로 일상과 운동 활력 관리에 최적임
-피로 개선 체감 — 아침 기상 시 몸이 가볍고 운동 집중도가 향상됨
-쇼핑백 동봉 선물성 — 쇼핑백이 포함되어 지인이나 동료 선물용으로 적합함</t>
+          <t>맛있고 부담 없는 풍미 — 매실 맛 등 맛과 향이 좋아 운동 중 물 대신 마시기 편함
+잘 풀리는 가루 제형 — 가루가 뭉치지 않고 잘 풀어져 음용 시 편리함
+운동 효과 체감 상승 — 섭취 시 전해질 보충 및 수행 능력 향상 차이가 크게 느껴짐</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>비리지 않은 맛 — 단백질 특유의 텁텁함이나 비린 맛 없이 초코우유처럼 달콤함
-간편한 포만감 — 운동 후나 간식 대용으로 간편하게 마시기 좋고 배가 든든함
-선물용 호응도 — 지인 및 부모님 운동 선물용으로 호불호 없이 만족도가 높음</t>
+          <t>확실한 활력 및 피로 개선 — 아침 피로감이 줄어들고 운동 집중도 및 하루 활력이 향상됨
+알찬 2개월분 세트 구성 — 아르기닌과 밀크씨슬을 함께 챙길 수 있는 효율적인 구성임</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>다양한 맛 구성 — 소시지 및 여러 양념 맛이 포함되어 물리지 않고 식사 가능함
-실용적인 보냉백 — 도시락 휴대가 가능한 넉넉한 크기의 보냉백을 증정함
-뛰어난 맛과 식감 — 퍽퍽하지 않고 일반 음식처럼 맛있게 즐길 수 있음</t>
+          <t>비린 맛 없는 달콤함 — 단백질 음료 특유의 비린 맛이나 텁텁함 없이 달콤하고 깔끔함
+든든한 포만감 제공 — 섭취 시 포만감이 느껴져 간식 대용이나 운동 후 마시기 좋음
+빠른 배송 및 증정 혜택 — 배송이 빠르고 추가 팩 증정이 있어 만족도가 높음</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화감 — 섭취 후 더부룩함이 완화되고 소화가 잘됨
-달콤한 옥수수맛 — 콘스프처럼 달콤하고 고소하여 거부감 없이 맛있음
-가성비 및 사은품 — 가격 대비 구성이 푸짐하고 씬칩 등 사은품 증정이 만족스러움</t>
+          <t>넉넉한 크기의 보냉백 증정 — 도시락용으로 들고 다니기 좋은 큼직한 보냉가방이 제공됨
+다양하고 풍부한 구성 — 여러 맛과 소세지 종류를 다양하게 체험할 수 있어 질리지 않음</t>
         </is>
       </c>
     </row>
@@ -4758,40 +4741,40 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 1포 용량 — 맛에 비해 1포당 용량이 다소 작게 느껴짐</t>
+          <t>다소 적은 내용물 양 — 맛은 좋으나 1포당 용량이 다소 적게 느껴짐</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>다소 비싼 가격 — 가격대가 높아 할인 행사 시기에만 구매하게 됨</t>
+          <t>비싼 가격대 — 가격대가 다소 높아 할인 기간에 구매를 선호하게 됨</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>가격 할인 아쉬움 — 지속적인 재구매를 위해 추가적인 가격 할인이 필요함</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
+          <t>한약재 특유의 맛 — 쌍화탕이나 한약재 같은 쓴맛이 포함되어 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>가격 할인 필요성 — 구매 부담을 줄이기 위한 세일 행사가 더 자주 요구됨</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>진한 한약재 맛 — 쌍화탕이나 한약 같은 쓴맛이 있어 호불호가 갈릴 수 있음</t>
+          <t>이물질(뼈) 혼입 발생 — 섭취 과정에서 단단한 뼈 조각이 씹히는 현상이 발생함</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>쇼핑백 불량 배송 — 증정 쇼핑백에 손잡이 끈이 누락되어 배송됨</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>이물질(뼈) 발견 — 섭취 중 단단한 뼈 조각이 씹히는 문제 발생함</t>
-        </is>
-      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>쇼핑백 부품 누락 — 증정용 쇼핑백의 끈이 안 달려서 배송되는 경우가 있음</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>맛 변화 아쉬움 — 이전 구매분에 비해 맛에 다소 차이가 느껴짐</t>
+          <t>뼈 조각 혼입 문제 — 닭가슴살 제품 내부에서 단단한 뼈가 씹히는 경우가 있음</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4786,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>29,600원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -4813,42 +4796,42 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>33,200원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>43,900원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>17,900원</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>33,200원</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>27,900원</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>25,900원</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>28,900원</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>25,900원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>23,900원</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5021,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5046,53 +5029,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602124&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911101&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251216/mSQXyRQCV8ORV8edPm4n613602124_00_01mSQXyRQCV8ORV8edPm4n.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/BQeSyYNH21gmMrEclYYV610911101_00_01BQeSyYNH21gmMrEclYYV.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1932</v>
+        <v>227</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>간편한 올인원 섭취 — 액상과 정제를 함께 먹을 수 있어 물 없이도 간편함</t>
+          <t>강렬한 목 청량감 — 캡슐이 터지면서 목구멍까지 시원하고 상쾌해짐</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>피로 회복 도움 — 커피 대용으로 마시기 좋으며 섭취 후 활력과 기운이 남</t>
+          <t>효과적인 구취 제거 — 식후나 외출 전 입안 텁텁함과 입냄새를 잘 잡아줌</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>상큼한 맛과 목넘김 — 상큼한 맛에 목넘김이 부드럽고 깔끔함</t>
+          <t>저렴한 가성비 — 다른 판매처 대비 가격이 저렴하여 부담 없이 구매 가능함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>유명 제품과의 맛 차이 — 타사 유명 멀티비타민 액상과 맛이 다름</t>
+          <t>아쉬운 상쾌함 강도 — 스트롱 제품 명칭에 비해 상쾌함이 다소 덜하게 느껴질 수 있음</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -5101,7 +5084,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5109,54 +5092,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/dxtu28UFPhWKbi5IG3n8613602130_00_01dxtu28UFPhWKbi5IG3n8.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>1657</v>
+        <v>232</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>맛있는 구미 제형 — 달콤하고 쫄깃쫄깃하여 간식처럼 맛있게 섭취 가능함</t>
+          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 간편하게 구매할 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>아이 섭취 편의 — 아이들이 거부감 없이 스스로 잘 찾아 먹음</t>
+          <t>속 냄새 제거 및 기분 전환 — 양치 후 텁텁함이나 음식 섭취 후 속에서 올라오는 냄새를 케어함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>두꺼운 캡슐 및 짧은 지속력 — 캡슐 껍질이 살짝 두꺼워 목에 걸릴 수 있고 지속 시간이 짧음</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5164,7 +5151,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5174,33 +5161,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3656</v>
+        <v>6810</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>우수한 가격 경쟁력 — 저렴한 가격으로 부담 없이 건강을 챙길 수 있음</t>
+          <t>최고의 가성비 — 저렴한 가격으로 부담 없이 꾸준히 구매하기 좋음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>위생적인 개별 포장 — 정제가 하나씩 개별 PTP 포장되어 보관 및 휴대가 편리함</t>
+          <t>편리한 복용 및 높은 만족도 — 사용하기 편리하여 부모님의 만족도가 높고 재구매율이 높음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -5211,7 +5198,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5219,12 +5206,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5234,47 +5221,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>117</v>
+        <v>6682</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 5,000원이라는 저렴한 가격 대비 만족스러운 구성임</t>
+          <t>위생적인 개별 포장 — 하나씩 개별 패킹되어 보관 및 복용이 깔끔함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>기상 시 개운함 — 복용 후 몸이 따뜻해지고 아침 기상 시 한결 개운함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>간편한 환 제형 — 하루 한 알 간편하게 섭취 가능하고 맛이 진함</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>모호한 효능 체감 — 단기 복용 시 뚜렷한 효과를 즉각 체감하기 어려움</t>
-        </is>
-      </c>
+          <t>만족스러운 제품 가성비 — 다이소 필 수 구매 아이템으로 꾸준히 복용하기 좋음</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5282,12 +5261,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5297,28 +5276,28 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/jrLxfLkWCczsCAsnqLoJ613602131_00_01jrLxfLkWCczsCAsnqLoJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1022</v>
+        <v>7226</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>상큼한 레몬맛 — 상큼한 레몬맛 구미로 아이부터 어른까지 맛있게 섭취 가능함</t>
+          <t>우수한 가격 경쟁력 — 다른 곳보다 가격이 저렴하여 부담 없이 복용 가능함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>면역 및 건강 관리 — 환절기 면역력 증진 및 비타민 보충용으로 먹기 편함</t>
+          <t>편리한 복용 방식 — 먹기 편리하여 혈당 및 일상 건강 관리용으로 적합함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -5329,7 +5308,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5337,12 +5316,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 베르베린 500 30정 30일분</t>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5352,36 +5331,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000206&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953535&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/MYOwtzQEETqQTroQjYz5600000206_00_00MYOwtzQEETqQTroQjYz5.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/nv6m1SoKa2Zw57OA3JHL994953535_00_00nv6m1SoKa2Zw57OA3JHL.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.7</v>
       </c>
       <c r="J7" t="n">
-        <v>868</v>
+        <v>1101</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>작은 알약 크기 — 정제 크기가 크지 않아 목넘김이 수월함</t>
+          <t>거부감 없는 달콤한 맛 — 달달한 꿀물 같아서 맛이 거북하지 않고 맛있음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>휴대성 및 가성비 — 외출이나 여행 시 챙기기 간편하고 가격 부담이 없음</t>
+          <t>간편한 복용과 제품 성능 — 먹기 편리하고 꾸준히 복용했을 때 성능 만족도가 높음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>강한 쓴맛 부담 — 정제 특유의 쓴맛이 강하게 느껴져 복용이 힘듦</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -5396,56 +5371,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[식후 혈당] 동화 배러크런치 바나바 요구르트맛 30정 10일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678608&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260825/oxNqPxCfU3Tre5j0PQQk601678608_00_02oxNqPxCfU3Tre5j0PQQk.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>141</v>
+        <v>863</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>식후 졸음 완화 — 식후 섭취 시 나른함이나 졸림이 덜한 느낌을 받음</t>
+          <t>즉각적인 활력 제공 — 섭취 시 기운이 나며 피로 완화 및 졸음운전 방지용으로 적합함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>간편한 캔디형 제형 — 요구르트맛 캔디처럼 씹어 먹을 수 있어 섭취가 간편함</t>
+          <t>높은 가성비와 휴대성 — 가격이 저렴하고 간편하게 휴대하며 생각날 때 먹기 편함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>기대 이하의 맛 — 요구르트 맛보다 특유의 약맛이 강해 거부감이 있음</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>생각보다 큰 크기 — 예상보다 정제 크기가 커서 씹어 먹기 다소 부담스러움</t>
-        </is>
-      </c>
+          <t>체감 효과 미흡 — 사람에 따라 별다른 효과를 느끼지 못할 수 있음</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
@@ -5459,54 +5430,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 블랙마카 60정 30일분</t>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000141&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/pBer8sS0SwGqVuRcsAKY600000141_00_00pBer8sS0SwGqVuRcsAKY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>960</v>
+        <v>554</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 — 저렴한 가격으로 꾸준히 활력 관리를 할 수 있음</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>높은 재구매 만족도 — 몸 관리를 위해 여러 차례 재구매하여 복용 중임</t>
-        </is>
-      </c>
+          <t>배변 활동 지원 — 화장실을 가기 어려울 때 간혹 먹으면 도움이 됨</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>미미한 변비 해소 효과 — 변비 해소나 배변 활동 측면에서 뚜렷한 효과가 느껴지지 않음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5514,58 +5485,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>동국제약 마데카 저분자 콜라겐C</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910603&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250530/iFPtDwREEwh2EwWoojJJ610910603_00_01iFPtDwREEwh2EwWoojJJ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>721</v>
+        <v>1458</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>거부감 없는 맛 — 비린 맛 없이 맛있는 가루 타입이라 섭취하기 편함</t>
+          <t>혈당 스파이크 방지 — 혈당 스파이크를 예방해 주어 유지어터 관리용으로 좋음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>사무실 간편 섭취 — 사무실이나 일상에서 가볍게 챙겨 먹기 좋고 가성비가 우수함</t>
+          <t>빠른 배송 및 맛있는 풍미 — 배송이 빠르고 맛이 좋아 섭취하기 편리함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>효능 체감 부족 — 섭취 후 뚜렷한 변화나 효과를 느끼기 어려움</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5573,7 +5540,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
+          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5588,36 +5555,40 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762097&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602124&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250807/jJGIxkBNqg0FzVjNiyoV901762097_00_01jJGIxkBNqg0FzVjNiyoV.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251216/mSQXyRQCV8ORV8edPm4n613602124_00_01mSQXyRQCV8ORV8edPm4n.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1144</v>
+        <v>1932</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>진한 풍미와 깔끔한 맛 — 쓰기만 하지 않고 깔끔하며 홍삼의 깊은 풍미가 느껴짐</t>
+          <t>체력 및 활력 보충 — 피곤할 때 먹으면 기운이 나고 면역력 및 피로 회복에 도움을 줌</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>간편한 스틱 형태 — 개별 스틱형으로 언제 어디서나 바로 짜 먹기 편리함</t>
+          <t>상큼하고 깔끔한 맛 — 맛이 상큼하고 목넘김이 깔끔하여 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>피로 회복 및 가성비 — 피곤할 때 힘이 나며 장기간 복용하기에 가성비가 훌륭함</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>액상과 정제 일체형 편리성 — 한 번에 영양소를 챙길 수 있어 간편하고 일상 섭취에 용이함</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>유명 제품과의 맛 차이 — 비슷한 디자인의 유명 멀티비타민 제품과 맛이 상이함</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5732,52 +5703,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
         </is>
       </c>
     </row>
@@ -5789,12 +5760,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -5804,32 +5775,32 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5846,52 +5817,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>오브맘 비타민C＆E 하루구미 30일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 베르베린 500 30정 30일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[식후 혈당] 동화 배러크런치 바나바 요구르트맛 30정 10일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 블랙마카 60정 30일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>동국제약 마데카 저분자 콜라겐C</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
         </is>
       </c>
     </row>
@@ -5902,16 +5873,16 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
@@ -5920,13 +5891,13 @@
         <v>4.7</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.8</v>
@@ -5939,34 +5910,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>6810</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6682</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>7226</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1101</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>863</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>554</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1458</v>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>1932</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>1657</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>3656</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>117</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1022</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>868</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>960</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>721</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>1144</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -5977,69 +5948,67 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>간편한 올인원 섭취 — 액상과 정제를 함께 먹을 수 있어 물 없이도 간편함
-피로 회복 도움 — 커피 대용으로 마시기 좋으며 섭취 후 활력과 기운이 남
-상큼한 맛과 목넘김 — 상큼한 맛에 목넘김이 부드럽고 깔끔함</t>
+          <t>강렬한 목 청량감 — 캡슐이 터지면서 목구멍까지 시원하고 상쾌해짐
+효과적인 구취 제거 — 식후나 외출 전 입안 텁텁함과 입냄새를 잘 잡아줌
+저렴한 가성비 — 다른 판매처 대비 가격이 저렴하여 부담 없이 구매 가능함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 구미 제형 — 달콤하고 쫄깃쫄깃하여 간식처럼 맛있게 섭취 가능함
-아이 섭취 편의 — 아이들이 거부감 없이 스스로 잘 찾아 먹음</t>
+          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 간편하게 구매할 수 있음
+속 냄새 제거 및 기분 전환 — 양치 후 텁텁함이나 음식 섭취 후 속에서 올라오는 냄새를 케어함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>우수한 가격 경쟁력 — 저렴한 가격으로 부담 없이 건강을 챙길 수 있음
-위생적인 개별 포장 — 정제가 하나씩 개별 PTP 포장되어 보관 및 휴대가 편리함</t>
+          <t>최고의 가성비 — 저렴한 가격으로 부담 없이 꾸준히 구매하기 좋음
+편리한 복용 및 높은 만족도 — 사용하기 편리하여 부모님의 만족도가 높고 재구매율이 높음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 5,000원이라는 저렴한 가격 대비 만족스러운 구성임
-기상 시 개운함 — 복용 후 몸이 따뜻해지고 아침 기상 시 한결 개운함
-간편한 환 제형 — 하루 한 알 간편하게 섭취 가능하고 맛이 진함</t>
+          <t>위생적인 개별 포장 — 하나씩 개별 패킹되어 보관 및 복용이 깔끔함
+만족스러운 제품 가성비 — 다이소 필 수 구매 아이템으로 꾸준히 복용하기 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 레몬맛 — 상큼한 레몬맛 구미로 아이부터 어른까지 맛있게 섭취 가능함
-면역 및 건강 관리 — 환절기 면역력 증진 및 비타민 보충용으로 먹기 편함</t>
+          <t>우수한 가격 경쟁력 — 다른 곳보다 가격이 저렴하여 부담 없이 복용 가능함
+편리한 복용 방식 — 먹기 편리하여 혈당 및 일상 건강 관리용으로 적합함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>작은 알약 크기 — 정제 크기가 크지 않아 목넘김이 수월함
-휴대성 및 가성비 — 외출이나 여행 시 챙기기 간편하고 가격 부담이 없음</t>
+          <t>거부감 없는 달콤한 맛 — 달달한 꿀물 같아서 맛이 거북하지 않고 맛있음
+간편한 복용과 제품 성능 — 먹기 편리하고 꾸준히 복용했을 때 성능 만족도가 높음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>식후 졸음 완화 — 식후 섭취 시 나른함이나 졸림이 덜한 느낌을 받음
-간편한 캔디형 제형 — 요구르트맛 캔디처럼 씹어 먹을 수 있어 섭취가 간편함</t>
+          <t>즉각적인 활력 제공 — 섭취 시 기운이 나며 피로 완화 및 졸음운전 방지용으로 적합함
+높은 가성비와 휴대성 — 가격이 저렴하고 간편하게 휴대하며 생각날 때 먹기 편함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 — 저렴한 가격으로 꾸준히 활력 관리를 할 수 있음
-높은 재구매 만족도 — 몸 관리를 위해 여러 차례 재구매하여 복용 중임</t>
+          <t>배변 활동 지원 — 화장실을 가기 어려울 때 간혹 먹으면 도움이 됨</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 맛 — 비린 맛 없이 맛있는 가루 타입이라 섭취하기 편함
-사무실 간편 섭취 — 사무실이나 일상에서 가볍게 챙겨 먹기 좋고 가성비가 우수함</t>
+          <t>혈당 스파이크 방지 — 혈당 스파이크를 예방해 주어 유지어터 관리용으로 좋음
+빠른 배송 및 맛있는 풍미 — 배송이 빠르고 맛이 좋아 섭취하기 편리함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>진한 풍미와 깔끔한 맛 — 쓰기만 하지 않고 깔끔하며 홍삼의 깊은 풍미가 느껴짐
-간편한 스틱 형태 — 개별 스틱형으로 언제 어디서나 바로 짜 먹기 편리함
-피로 회복 및 가성비 — 피곤할 때 힘이 나며 장기간 복용하기에 가성비가 훌륭함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>체력 및 활력 보충 — 피곤할 때 먹으면 기운이 나고 면역력 및 피로 회복에 도움을 줌
+상큼하고 깔끔한 맛 — 맛이 상큼하고 목넘김이 깔끔하여 부담 없이 챙겨 먹기 좋음
+액상과 정제 일체형 편리성 — 한 번에 영양소를 챙길 수 있어 간편하고 일상 섭취에 용이함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -6047,35 +6016,34 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>유명 제품과의 맛 차이 — 타사 유명 멀티비타민 액상과 맛이 다름</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>아쉬운 상쾌함 강도 — 스트롱 제품 명칭에 비해 상쾌함이 다소 덜하게 느껴질 수 있음</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>두꺼운 캡슐 및 짧은 지속력 — 캡슐 껍질이 살짝 두꺼워 목에 걸릴 수 있고 지속 시간이 짧음</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>모호한 효능 체감 — 단기 복용 시 뚜렷한 효과를 즉각 체감하기 어려움</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>강한 쓴맛 부담 — 정제 특유의 쓴맛이 강하게 느껴져 복용이 힘듦</t>
-        </is>
-      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>기대 이하의 맛 — 요구르트 맛보다 특유의 약맛이 강해 거부감이 있음
-생각보다 큰 크기 — 예상보다 정제 크기가 커서 씹어 먹기 다소 부담스러움</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>효능 체감 부족 — 섭취 후 뚜렷한 변화나 효과를 느끼기 어려움</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>체감 효과 미흡 — 사람에 따라 별다른 효과를 느끼지 못할 수 있음</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>미미한 변비 해소 효과 — 변비 해소나 배변 활동 측면에서 뚜렷한 효과가 느껴지지 않음</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>유명 제품과의 맛 차이 — 비슷한 디자인의 유명 멀티비타민 제품과 맛이 상이함</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6085,47 +6053,47 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -6309,7 +6277,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6317,27 +6285,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,400원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786107ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6352,7 +6320,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6360,35 +6328,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>5,400원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>595</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786107ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -6399,7 +6363,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6407,27 +6371,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364590ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6442,7 +6406,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6450,35 +6414,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>리쥬란</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258641&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>354</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025864119ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -6489,7 +6449,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6497,46 +6457,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>리쥬란</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258641&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025864119ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 식감 — 탱글탱글하고 쫀득한 청포도 사과맛 젤리로 간식처럼 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>간편한 개별 포장 — 한 포씩 낱개 포장되어 외출이나 산책 시 챙겨 다니기 용이함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>기획 세트 증정 혜택 — 추가 증정이 포함된 넉넉한 구성으로 만족도가 높음</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -6544,7 +6492,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6552,40 +6500,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11,400원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1503</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>탄수화물 분해 관리 — 식후 탄수화물 컷팅 및 이너케어 루틴으로 챙기기 적합함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -6595,7 +6535,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6603,40 +6543,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246271&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627107ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>237</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>맛있는 복숭아맛 — 비린 맛에 민감한 입맛도 거부감 없이 맛있게 섭취 가능함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -6654,35 +6586,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>솔티스눈 프로텍션 프로 S3 20캡슐 (20일분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>솔티스</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12,800원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000234147&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023414702ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>141</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587422ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -6724,27 +6652,19 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>17365</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>얼굴 붓기 관리 — 야식이나 자극적인 음식 섭취 후 얼굴 땡땡함 완화에 효과적임</t>
+          <t>얼굴 붓기 관리 효과 — 자극적인 안주나 야식 섭취 후 얼굴 라인 정돈 및 붓기 제거에 효과적임</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>미니환 제형 목넘김 — 알약 크기가 작은 환 형태로 물과 함께 삼키기 수월함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>휴대 편의성 — 개별 포장으로 파우치나 가방에 휴대하여 중요 일정 전 챙기기 좋음</t>
-        </is>
-      </c>
+          <t>섭취하기 편한 미니환 — 작은 미니환 제형으로 물과 함께 쉽게 삼킬 수 있음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -6752,7 +6672,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6760,50 +6680,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263899&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>25812</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026389913ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>작고 가벼운 캡슐 — 캡슐 크기가 170mg으로 매우 작아 목넘김이 매우 수월함</t>
+          <t>상큼한 레몬라임 맛 — 레몬라임 맛 젤리스틱 형태로 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>질과 장 더블케어 — 여성 질 건강과 장 건강을 하루 한 알로 동시에 관리 가능함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>귀여운 기획 굿즈 — 포켓몬 콜라보 카드케이스 등 증정품 구성의 만족도가 높음</t>
-        </is>
-      </c>
+          <t>간편한 3중 성분 챙김 — 글루타치온, 히알루론산, 비타민C를 하루 한 포로 간편하게 관리 가능함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -6919,52 +6831,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
     </row>
@@ -6976,42 +6888,42 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>씨제이웰케어</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>리쥬란</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>리쥬란</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>딥트3일</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>솔티스</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -7021,7 +6933,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>온리추얼</t>
         </is>
       </c>
     </row>
@@ -7033,42 +6945,42 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>솔티스눈 프로텍션 프로 S3 20캡슐 (20일분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -7078,7 +6990,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
         </is>
       </c>
     </row>
@@ -7089,29 +7001,15 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -7120,31 +7018,17 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="n">
-        <v>595</v>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="n">
-        <v>354</v>
-      </c>
+      <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="n">
-        <v>1503</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>17365</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>25812</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7154,36 +7038,20 @@
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 식감 — 탱글탱글하고 쫀득한 청포도 사과맛 젤리로 간식처럼 섭취 가능함
-간편한 개별 포장 — 한 포씩 낱개 포장되어 외출이나 산책 시 챙겨 다니기 용이함
-기획 세트 증정 혜택 — 추가 증정이 포함된 넉넉한 구성으로 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>탄수화물 분해 관리 — 식후 탄수화물 컷팅 및 이너케어 루틴으로 챙기기 적합함</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 복숭아맛 — 비린 맛에 민감한 입맛도 거부감 없이 맛있게 섭취 가능함</t>
-        </is>
-      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>얼굴 붓기 관리 — 야식이나 자극적인 음식 섭취 후 얼굴 땡땡함 완화에 효과적임
-미니환 제형 목넘김 — 알약 크기가 작은 환 형태로 물과 함께 삼키기 수월함
-휴대 편의성 — 개별 포장으로 파우치나 가방에 휴대하여 중요 일정 전 챙기기 좋음</t>
+          <t>얼굴 붓기 관리 효과 — 자극적인 안주나 야식 섭취 후 얼굴 라인 정돈 및 붓기 제거에 효과적임
+섭취하기 편한 미니환 — 작은 미니환 제형으로 물과 함께 쉽게 삼킬 수 있음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>작고 가벼운 캡슐 — 캡슐 크기가 170mg으로 매우 작아 목넘김이 매우 수월함
-질과 장 더블케어 — 여성 질 건강과 장 건강을 하루 한 알로 동시에 관리 가능함
-귀여운 기획 굿즈 — 포켓몬 콜라보 카드케이스 등 증정품 구성의 만족도가 높음</t>
+          <t>상큼한 레몬라임 맛 — 레몬라임 맛 젤리스틱 형태로 맛있게 먹기 좋음
+간편한 3중 성분 챙김 — 글루타치온, 히알루론산, 비타민C를 하루 한 포로 간편하게 관리 가능함</t>
         </is>
       </c>
     </row>
@@ -7212,42 +7080,42 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>5,400원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>18,800원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>35,800원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>31,400원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>26,800원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>19,900원</t>
-        </is>
-      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>11,400원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>12,800원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -7257,7 +7125,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>17,900원</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7387,82 +7255,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -7471,42 +7339,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7515,29 +7383,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
         <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7547,12 +7415,56 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
